--- a/data/trans_dic/P1801_2016_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1801_2016_2023-Habitat-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>53,42%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>45,46; 53,05</t>
+          <t>45,44; 53,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47,12; 55,8</t>
+          <t>46,56; 54,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57,57; 65,19</t>
+          <t>57,79; 65,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53,23; 59,41</t>
+          <t>53,15; 59,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,59; 58,12</t>
+          <t>52,52; 57,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,46; 56,86</t>
+          <t>50,89; 55,97</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>53,45%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>41,12; 47,9</t>
+          <t>41,34; 47,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>49,52; 82,11</t>
+          <t>45,4; 52,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53,0; 59,33</t>
+          <t>53,27; 59,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55,78; 61,31</t>
+          <t>55,15; 60,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>48,35; 52,66</t>
+          <t>47,97; 52,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,78; 72,97</t>
+          <t>51,14; 55,77</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>44,66%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42,45; 50,1</t>
+          <t>42,72; 50,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36,65; 45,16</t>
+          <t>36,06; 44,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56,54; 63,11</t>
+          <t>56,21; 63,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>44,33; 78,21</t>
+          <t>45,72; 52,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>50,5; 55,85</t>
+          <t>50,55; 55,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,95; 68,37</t>
+          <t>42,1; 47,4</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>55,31%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>43,64; 50,21</t>
+          <t>43,56; 49,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>49,21; 56,24</t>
+          <t>48,07; 54,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50,07; 56,35</t>
+          <t>50,06; 56,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44,7; 60,77</t>
+          <t>55,72; 61,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>48,03; 52,57</t>
+          <t>47,99; 52,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,77; 57,26</t>
+          <t>53,06; 57,49</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>52,03%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>44,71; 48,26</t>
+          <t>44,91; 48,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>48,68; 64,44</t>
+          <t>46,08; 49,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55,48; 58,78</t>
+          <t>55,38; 58,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53,4; 64,75</t>
+          <t>54,36; 57,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>50,62; 53,11</t>
+          <t>50,81; 53,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,85; 61,18</t>
+          <t>50,92; 53,3</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>327805</t>
+          <t>349910</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>381614</t>
+          <t>410360</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>709419</t>
+          <t>760271</t>
         </is>
       </c>
     </row>
@@ -1182,32 +1182,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>306770; 357952</t>
+          <t>306661; 359881</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>299411; 354588</t>
+          <t>321585; 379701</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>387362; 438621</t>
+          <t>388835; 439247</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>359436; 401150</t>
+          <t>389373; 432388</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>708707; 783243</t>
+          <t>707802; 777977</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>674532; 745203</t>
+          <t>724317; 796655</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>722059</t>
+          <t>509539</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>559657</t>
+          <t>622446</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1281716</t>
+          <t>1131985</t>
         </is>
       </c>
     </row>
@@ -1300,32 +1300,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>420436; 489741</t>
+          <t>422645; 486052</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>590268; 978648</t>
+          <t>475758; 545410</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>552717; 618771</t>
+          <t>555514; 620963</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>533946; 586857</t>
+          <t>590035; 650531</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>998532; 1087567</t>
+          <t>990803; 1088136</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1155743; 1568152</t>
+          <t>1083008; 1181201</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>286919</t>
+          <t>322515</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>537172</t>
+          <t>397119</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>824090</t>
+          <t>719634</t>
         </is>
       </c>
     </row>
@@ -1418,32 +1418,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>322447; 380510</t>
+          <t>324514; 380816</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>257889; 317754</t>
+          <t>289157; 353157</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>443817; 495447</t>
+          <t>441277; 499279</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>413182; 728888</t>
+          <t>370018; 424710</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>780031; 862634</t>
+          <t>780812; 864476</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>686159; 1118227</t>
+          <t>678406; 763789</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>490040</t>
+          <t>509697</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>609811</t>
+          <t>654638</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1099851</t>
+          <t>1164335</t>
         </is>
       </c>
     </row>
@@ -1536,32 +1536,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>409130; 470740</t>
+          <t>408360; 468670</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>455470; 520509</t>
+          <t>475381; 542390</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>522601; 588181</t>
+          <t>522501; 591452</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>488112; 663505</t>
+          <t>621838; 683786</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>951690; 1041629</t>
+          <t>950872; 1042577</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>963781; 1155222</t>
+          <t>1116971; 1210190</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1826823</t>
+          <t>1691660</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2088253</t>
+          <t>2084564</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3915075</t>
+          <t>3776224</t>
         </is>
       </c>
     </row>
@@ -1654,32 +1654,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1517483; 1638137</t>
+          <t>1524395; 1638978</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1682575; 2227435</t>
+          <t>1626326; 1757140</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1966592; 2083332</t>
+          <t>1962823; 2088270</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1952295; 2367460</t>
+          <t>2026244; 2136118</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3512610; 3685006</t>
+          <t>3525518; 3700078</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3688333; 4351924</t>
+          <t>3695188; 3868475</t>
         </is>
       </c>
     </row>
